--- a/website/examples/example_odk_calibrated_scale_MinMax.xlsx
+++ b/website/examples/example_odk_calibrated_scale_MinMax.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" r:id="R9e3bc5ad9ff74965"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" r:id="R724da5d0d52e4b82"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" r:id="R2207f96ec30c42d6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" r:id="R013692cce48c428a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" r:id="R4d7069877bff4255"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" r:id="R17d88ac1bab94247"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -567,7 +567,7 @@
         <x:v>field-list</x:v>
       </x:c>
       <x:c r="I3" t="str">
-        <x:v>com.example.researchos.EXECUTE_METHOD(method_id='calibrated_scale',input_prompt='Rate your pain',input_hint='0 means no pain; 100 means the worst pain you can imagine',input_vas_length_mm='50',input_minimum='0',input_maximum='10',return_mode='flat')</x:v>
+        <x:v>com.example.methodmesh.EXECUTE_METHOD(method_id='calibrated_scale',input_prompt='Rate your pain',input_hint='0 means no pain; 100 means the worst pain you can imagine',input_vas_length_mm='50',input_minimum='0',input_maximum='10',return_mode='flat')</x:v>
       </x:c>
       <x:c r="J3"/>
       <x:c r="K3"/>
@@ -619,10 +619,10 @@
         <x:v>text</x:v>
       </x:c>
       <x:c r="B6" t="str">
-        <x:v>researchos_execution_id</x:v>
+        <x:v>methodmesh_execution_id</x:v>
       </x:c>
       <x:c r="C6" t="str">
-        <x:v>ResearchOS execution ID</x:v>
+        <x:v>MethodMesh execution ID</x:v>
       </x:c>
       <x:c r="D6"/>
       <x:c r="E6"/>
@@ -640,10 +640,10 @@
         <x:v>text</x:v>
       </x:c>
       <x:c r="B7" t="str">
-        <x:v>researchos_status</x:v>
+        <x:v>methodmesh_status</x:v>
       </x:c>
       <x:c r="C7" t="str">
-        <x:v>ResearchOS status</x:v>
+        <x:v>MethodMesh status</x:v>
       </x:c>
       <x:c r="D7"/>
       <x:c r="E7"/>
